--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484796_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484796_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.215</v>
+        <v>5.8017</v>
       </c>
       <c r="E2" t="n">
-        <v>1.577</v>
+        <v>2.0843</v>
       </c>
       <c r="F2" t="n">
-        <v>3.638</v>
+        <v>3.7174</v>
       </c>
       <c r="G2" t="n">
         <v>2.2602</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1017</v>
+        <v>0.485</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1735</v>
+        <v>0.3338</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0718</v>
+        <v>0.1512</v>
       </c>
       <c r="V2" t="n">
         <v>2.4904</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5403</v>
+        <v>4.4908</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2183</v>
+        <v>2.4333</v>
       </c>
       <c r="F3" t="n">
-        <v>2.322</v>
+        <v>2.0574</v>
       </c>
       <c r="G3" t="n">
         <v>1.8959</v>
@@ -688,13 +688,13 @@
         <v>1.3209</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3427</v>
+        <v>1.2931</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4884</v>
+        <v>0.7034</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8542</v>
+        <v>0.5897</v>
       </c>
       <c r="V3" t="n">
         <v>1.8678</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3493</v>
+        <v>3.503</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5498</v>
+        <v>0.8623</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7995</v>
+        <v>2.6407</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8096</v>
@@ -766,13 +766,13 @@
         <v>1.887</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3668</v>
+        <v>1.5205</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6307</v>
+        <v>0.9431</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7361</v>
+        <v>0.5774</v>
       </c>
       <c r="V4" t="n">
         <v>3.7356</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8106</v>
+        <v>2.8199</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3844</v>
+        <v>0.6582</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4262</v>
+        <v>2.1616</v>
       </c>
       <c r="G5" t="n">
         <v>4.3556</v>
@@ -844,13 +844,13 @@
         <v>1.887</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3427</v>
+        <v>1.3519</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4543</v>
+        <v>0.7281</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8884</v>
+        <v>0.6238</v>
       </c>
       <c r="V5" t="n">
         <v>1.8298</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2363</v>
+        <v>1.4538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1557</v>
+        <v>0.2145</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0805</v>
+        <v>1.2393</v>
       </c>
       <c r="G6" t="n">
         <v>2.0381</v>
@@ -922,13 +922,13 @@
         <v>0.7548</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6131</v>
+        <v>0.8306</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3215</v>
+        <v>0.3803</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2916</v>
+        <v>0.4503</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2262</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CARR</t>
+          <t>H. RIVAS OSETE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.516</v>
+        <v>0.2775</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-1.9051</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0679</v>
+        <v>2.1826</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.956</v>
+        <v>-0.1272</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.0842</v>
+        <v>1.1935</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1282</v>
+        <v>-1.3207</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5485</v>
+        <v>-1.1935</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.4817</v>
+        <v>0.1057</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9331</v>
+        <v>-1.2991</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4074</v>
+        <v>1.0663</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6026</v>
+        <v>1.0878</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1951</v>
+        <v>-0.0216</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.3966</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.7175</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>2.68</v>
+        <v>0.4424</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2237</v>
+        <v>0.2319</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4562</v>
+        <v>0.2105</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1886</v>
+        <v>0.3398</v>
       </c>
       <c r="W7" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. RIVAS OSETE</t>
+          <t>E. RHAIEM SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2607</v>
+        <v>-0.132</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7102</v>
+        <v>-1.0107</v>
       </c>
       <c r="F8" t="n">
-        <v>1.971</v>
+        <v>0.8788</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1272</v>
+        <v>-0.5204</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1935</v>
+        <v>-0.9297</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3207</v>
+        <v>0.4093</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1935</v>
+        <v>-1.1312</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1057</v>
+        <v>-0.5228</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2991</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0663</v>
+        <v>0.6108</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0878</v>
+        <v>-0.4069</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0216</v>
+        <v>1.0177</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3774</v>
+        <v>0.9435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4256</v>
+        <v>0.3504</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4267</v>
+        <v>0.1205</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0012</v>
+        <v>0.2299</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3398</v>
+        <v>-0.9054</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3398</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>J. CARR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6401</v>
+        <v>-0.3467</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9175</v>
+        <v>-1.4674</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2774</v>
+        <v>1.1208</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1176</v>
+        <v>-0.956</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.468</v>
+        <v>-3.0842</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6496</v>
+        <v>2.1282</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5137</v>
+        <v>-0.5485</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2146</v>
+        <v>-2.4817</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2991</v>
+        <v>1.9331</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3962</v>
+        <v>-0.4074</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7466</v>
+        <v>-0.6026</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6496</v>
+        <v>0.1951</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5096</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-4.7175</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7419</v>
+        <v>1.8173</v>
       </c>
       <c r="T9" t="n">
-        <v>0.238</v>
+        <v>1.3082</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5038</v>
+        <v>0.5091</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2452</v>
+        <v>2.1886</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2452</v>
+        <v>2.4904</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. RHAIEM SANCHEZ</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8186</v>
+        <v>-0.9349</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4593</v>
+        <v>-3.0536</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6407</v>
+        <v>2.1187</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5204</v>
+        <v>-1.1176</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9297</v>
+        <v>-0.468</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4093</v>
+        <v>-0.6496</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1312</v>
+        <v>-2.5137</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5228</v>
+        <v>-1.2146</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-1.2991</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6108</v>
+        <v>1.3962</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4069</v>
+        <v>0.7466</v>
       </c>
       <c r="O10" t="n">
-        <v>1.0177</v>
+        <v>0.6496</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9435</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q10" t="n">
+        <v>-1.887</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.2452</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2452</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.9435</v>
-      </c>
-      <c r="S10" t="n">
-        <v>-0.3362</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-0.3281</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.008200000000000001</v>
-      </c>
-      <c r="V10" t="n">
-        <v>-0.9054</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.9054</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6398</v>
+        <v>-7.2215</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.484</v>
+        <v>-7.1716</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1558</v>
+        <v>-0.0499</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7712</v>
@@ -1312,13 +1312,13 @@
         <v>0.7548</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.4177</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0617</v>
+        <v>0.3741</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0623</v>
+        <v>0.0436</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8488</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.829699999999999</v>
+        <v>9.711600000000004</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.2377</v>
+        <v>-8.3558</v>
       </c>
       <c r="F12" t="n">
         <v>18.0674</v>
@@ -1360,22 +1360,22 @@
         <v>-5.6034</v>
       </c>
       <c r="I12" t="n">
-        <v>9.851099999999999</v>
+        <v>9.851100000000001</v>
       </c>
       <c r="J12" t="n">
         <v>-3.6149</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.345300000000001</v>
+        <v>-5.3453</v>
       </c>
       <c r="L12" t="n">
-        <v>1.730399999999999</v>
+        <v>1.7304</v>
       </c>
       <c r="M12" t="n">
         <v>7.8629</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2580999999999998</v>
+        <v>-0.2580999999999997</v>
       </c>
       <c r="O12" t="n">
         <v>8.120700000000001</v>
@@ -1390,16 +1390,16 @@
         <v>11.322</v>
       </c>
       <c r="S12" t="n">
-        <v>8.074299999999999</v>
+        <v>8.956</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3434</v>
+        <v>5.2254</v>
       </c>
       <c r="U12" t="n">
-        <v>3.730399999999999</v>
+        <v>3.7306</v>
       </c>
       <c r="V12" t="n">
-        <v>9.716799999999999</v>
+        <v>9.716800000000001</v>
       </c>
       <c r="W12" t="n">
         <v>14.5646</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1082</v>
+        <v>3.3829</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6336</v>
+        <v>1.347</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4746</v>
+        <v>2.0358</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5948</v>
+        <v>3.6746</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1454</v>
+        <v>2.1874</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5506</v>
+        <v>1.4872</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5517</v>
+        <v>2.75</v>
       </c>
       <c r="K13" t="n">
-        <v>3.0591</v>
+        <v>0.8084</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.5075</v>
+        <v>1.9416</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0432</v>
+        <v>0.9245</v>
       </c>
       <c r="N13" t="n">
-        <v>1.0863</v>
+        <v>1.379</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0431</v>
+        <v>-0.4544</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R13" t="n">
-        <v>4.1514</v>
+        <v>3.0192</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3356</v>
+        <v>-1.1222</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0871</v>
+        <v>-0.7613</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2485</v>
+        <v>-0.3609</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5846</v>
+        <v>-1.2452</v>
       </c>
       <c r="W13" t="n">
-        <v>3.0561</v>
+        <v>0.3018</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4714</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3653</v>
+        <v>3.2489</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9573</v>
+        <v>1.1465</v>
       </c>
       <c r="F14" t="n">
-        <v>1.408</v>
+        <v>2.1024</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6746</v>
+        <v>1.5948</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1874</v>
+        <v>4.1454</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4872</v>
+        <v>-2.5506</v>
       </c>
       <c r="J14" t="n">
-        <v>2.75</v>
+        <v>0.5517</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8084</v>
+        <v>3.0591</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9416</v>
+        <v>-2.5075</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9245</v>
+        <v>1.0432</v>
       </c>
       <c r="N14" t="n">
-        <v>1.379</v>
+        <v>1.0863</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4544</v>
+        <v>-0.0431</v>
       </c>
       <c r="P14" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0192</v>
+        <v>4.1514</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1398</v>
+        <v>-1.195</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1511</v>
+        <v>-0.5743</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9887</v>
+        <v>-0.6207</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2452</v>
+        <v>0.5846</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3018</v>
+        <v>3.0561</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.547</v>
+        <v>-2.4714</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2442</v>
+        <v>0.619</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1806</v>
+        <v>-1.3755</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4248</v>
+        <v>1.9945</v>
       </c>
       <c r="G15" t="n">
         <v>1.2455</v>
@@ -1624,13 +1624,13 @@
         <v>4.3401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3569</v>
+        <v>-0.2684</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2635</v>
+        <v>-0.4583</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6203</v>
+        <v>0.19</v>
       </c>
       <c r="V15" t="n">
         <v>-2.8112</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4679</v>
+        <v>-0.4799</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8522</v>
+        <v>-1.0471</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3844</v>
+        <v>0.5672</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5256</v>
@@ -1702,13 +1702,13 @@
         <v>0.7548</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0012</v>
+        <v>-0.0109</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0617</v>
+        <v>-0.1332</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0605</v>
+        <v>0.1223</v>
       </c>
       <c r="V16" t="n">
         <v>0.3018</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2277</v>
+        <v>-0.7165</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0747</v>
+        <v>-0.5875</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.153</v>
+        <v>-0.1289</v>
       </c>
       <c r="G17" t="n">
         <v>1.4457</v>
@@ -1780,13 +1780,13 @@
         <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.3511</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8107</v>
+        <v>-0.3235</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0517</v>
+        <v>-0.0276</v>
       </c>
       <c r="V17" t="n">
         <v>-3.132</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. KOVAL</t>
+          <t>F. LOPEZ ZOROA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.754</v>
+        <v>-1.4895</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2545</v>
+        <v>-2.6282</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5006</v>
+        <v>1.1387</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8004</v>
+        <v>-2.8656</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3498</v>
+        <v>-0.2027</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4506</v>
+        <v>-2.6629</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.843</v>
+        <v>-2.7509</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.8022</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2991</v>
+        <v>-1.9487</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0426</v>
+        <v>-0.1148</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1941</v>
+        <v>0.5995</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1515</v>
+        <v>-0.7143</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.897</v>
+        <v>-1.0959</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4115</v>
+        <v>-0.4999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4855</v>
+        <v>-0.596</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.6226</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. LOPEZ ZOROA</t>
+          <t>O. KOVAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2388</v>
+        <v>-1.5591</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.1153</v>
+        <v>-2.0597</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.5006</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8656</v>
+        <v>-1.8004</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2027</v>
+        <v>-0.3498</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.6629</v>
+        <v>-1.4506</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.7509</v>
+        <v>-1.843</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8022</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.9487</v>
+        <v>-1.2991</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1148</v>
+        <v>0.0426</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5995</v>
+        <v>0.1941</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7143</v>
+        <v>-0.1515</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4531</v>
+        <v>0.9435</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8453</v>
+        <v>-0.7022</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9871</v>
+        <v>-0.2166</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8582</v>
+        <v>-0.4855</v>
       </c>
       <c r="V19" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6226</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6405</v>
+        <v>-2.1798</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.1133</v>
+        <v>-6.0159</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4728</v>
+        <v>3.8361</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4006</v>
@@ -2014,13 +2014,13 @@
         <v>3.3966</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4097</v>
+        <v>-0.9489</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5726</v>
+        <v>-0.4752</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.837</v>
+        <v>-0.4737</v>
       </c>
       <c r="V20" t="n">
         <v>0.6036</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.2186</v>
+        <v>-7.7071</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.0675</v>
+        <v>-6.847</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1511</v>
+        <v>-0.8601</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6161</v>
@@ -2092,13 +2092,13 @@
         <v>3.2079</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0575</v>
+        <v>-0.4309</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4913</v>
+        <v>-0.2881</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4338</v>
+        <v>-0.1428</v>
       </c>
       <c r="V21" t="n">
         <v>-4.0374</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.829800000000001</v>
+        <v>-6.8811</v>
       </c>
       <c r="E22" t="n">
-        <v>-18.0672</v>
+        <v>-18.0674</v>
       </c>
       <c r="F22" t="n">
-        <v>9.2376</v>
+        <v>11.1863</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2477</v>
@@ -2143,13 +2143,13 @@
         <v>-9.8512</v>
       </c>
       <c r="J22" t="n">
-        <v>-7.8626</v>
+        <v>-7.862600000000001</v>
       </c>
       <c r="K22" t="n">
         <v>0.2580999999999991</v>
       </c>
       <c r="L22" t="n">
-        <v>-8.120899999999999</v>
+        <v>-8.120900000000001</v>
       </c>
       <c r="M22" t="n">
         <v>3.6149</v>
@@ -2170,13 +2170,13 @@
         <v>24.531</v>
       </c>
       <c r="S22" t="n">
-        <v>-8.074200000000001</v>
+        <v>-6.125500000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.7306</v>
+        <v>-3.7304</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.343599999999999</v>
+        <v>-2.3949</v>
       </c>
       <c r="V22" t="n">
         <v>-9.716799999999999</v>
